--- a/data/trans_bre/IP18A02-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP18A02-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 32,28</t>
+          <t>2,27; 32,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 9,75</t>
+          <t>-10,91; 10,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,85; 1,43</t>
+          <t>-20,75; 1,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 32,98</t>
+          <t>-6,86; 29,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 167,46</t>
+          <t>5,04; 166,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-64,56; 110,72</t>
+          <t>-55,45; 114,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-73,71; 12,47</t>
+          <t>-72,18; 14,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 4,55</t>
+          <t>-11,26; 4,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 10,68</t>
+          <t>-5,07; 10,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 5,02</t>
+          <t>-12,54; 3,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 25,09</t>
+          <t>-12,6; 21,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,16; 47,27</t>
+          <t>-57,68; 41,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,65; 153,32</t>
+          <t>-36,51; 142,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-60,87; 49,69</t>
+          <t>-61,98; 43,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-81,86; 432,59</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 8,89</t>
+          <t>-13,53; 8,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 17,32</t>
+          <t>-5,33; 17,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 20,7</t>
+          <t>0,35; 20,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,18; 9,62</t>
+          <t>-21,77; 9,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-50,89; 55,76</t>
+          <t>-51,43; 51,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-24,04; 142,36</t>
+          <t>-23,34; 140,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 401,32</t>
+          <t>-13,4; 430,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 13,75</t>
+          <t>-9,75; 13,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 16,71</t>
+          <t>0,02; 17,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 16,87</t>
+          <t>-3,22; 16,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 55,63</t>
+          <t>0,42; 53,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,82; 87,91</t>
+          <t>-38,55; 87,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 473,22</t>
+          <t>-8,48; 486,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,34; 309,79</t>
+          <t>-27,24; 289,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,86; —</t>
+          <t>-56,6; —</t>
         </is>
       </c>
     </row>
@@ -1060,37 +1060,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,59; 17,56</t>
+          <t>-17,34; 16,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-26,13; -0,78</t>
+          <t>-26,67; -2,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 13,64</t>
+          <t>-18,75; 11,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-55,66; 0,0</t>
+          <t>-61,67; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-59,94; 128,48</t>
+          <t>-59,64; 121,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-92,5; 19,41</t>
+          <t>-93,19; -1,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-51,2; 65,79</t>
+          <t>-50,67; 51,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,49 +1160,49 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 14,11</t>
+          <t>-11,26; 13,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 22,9</t>
+          <t>-3,14; 23,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 11,66</t>
+          <t>-10,58; 11,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 8,89</t>
+          <t>-24,72; 10,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,55; 98,61</t>
+          <t>-45,81; 100,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 248,89</t>
+          <t>-18,34; 240,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-56,48; 150,17</t>
+          <t>-56,3; 159,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 230,01</t>
+          <t>-100,0; 300,89</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 13,91</t>
+          <t>-3,6; 13,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 11,44</t>
+          <t>-6,75; 10,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,29; 5,21</t>
+          <t>-13,51; 6,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-23,2; 15,85</t>
+          <t>-24,18; 18,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-16,01; 77,43</t>
+          <t>-13,39; 78,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,27; 52,82</t>
+          <t>-23,22; 49,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-39,32; 22,97</t>
+          <t>-38,32; 29,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-80,96; 136,67</t>
+          <t>-78,13; 194,56</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 12,62</t>
+          <t>-3,15; 12,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 7,47</t>
+          <t>-8,88; 7,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 6,39</t>
+          <t>-8,1; 6,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-25,67; 30,66</t>
+          <t>-26,33; 32,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 91,48</t>
+          <t>-14,47; 89,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-28,43; 32,06</t>
+          <t>-29,19; 33,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,07; 32,56</t>
+          <t>-32,3; 31,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-44,76; 80,24</t>
+          <t>-46,98; 95,63</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 6,81</t>
+          <t>-0,7; 6,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 5,5</t>
+          <t>-1,39; 6,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 3,25</t>
+          <t>-3,93; 2,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 10,24</t>
+          <t>-8,02; 8,7</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 38,51</t>
+          <t>-3,08; 37,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 32,42</t>
+          <t>-6,93; 35,59</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-18,97; 19,2</t>
+          <t>-18,51; 15,8</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-35,11; 69,03</t>
+          <t>-35,03; 56,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A02-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP18A02-Provincia-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 32,2</t>
+          <t>2,24; 32,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 10,92</t>
+          <t>-11,26; 10,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,75; 1,82</t>
+          <t>-21,94; 1,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 29,29</t>
+          <t>-7,33; 34,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,04; 166,53</t>
+          <t>6,33; 168,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-55,45; 114,4</t>
+          <t>-56,99; 131,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-72,18; 14,37</t>
+          <t>-72,74; 14,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 4,35</t>
+          <t>-10,74; 4,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 10,43</t>
+          <t>-5,05; 10,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 3,92</t>
+          <t>-11,94; 5,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 21,87</t>
+          <t>-13,23; 22,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,68; 41,94</t>
+          <t>-55,56; 38,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,51; 142,84</t>
+          <t>-39,46; 134,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-61,98; 43,11</t>
+          <t>-60,77; 46,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-81,86; 432,59</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 8,62</t>
+          <t>-12,7; 9,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 17,56</t>
+          <t>-4,52; 17,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 20,59</t>
+          <t>0,8; 20,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,77; 9,91</t>
+          <t>-20,11; 11,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-51,43; 51,64</t>
+          <t>-46,77; 58,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,34; 140,1</t>
+          <t>-22,11; 135,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 430,08</t>
+          <t>-1,51; 520,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 13,28</t>
+          <t>-9,13; 14,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,02; 17,55</t>
+          <t>0,02; 17,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 16,77</t>
+          <t>-3,06; 15,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 53,08</t>
+          <t>1,06; 52,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,55; 87,84</t>
+          <t>-36,14; 92,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 486,92</t>
+          <t>-4,52; 492,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,24; 289,22</t>
+          <t>-28,34; 276,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,6; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1060,37 +1060,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 16,06</t>
+          <t>-17,24; 15,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-26,67; -2,98</t>
+          <t>-26,49; -2,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 11,96</t>
+          <t>-19,15; 11,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-61,67; 0,0</t>
+          <t>-54,91; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-59,64; 121,68</t>
+          <t>-58,3; 113,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-93,19; -1,15</t>
+          <t>-92,49; 8,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-50,67; 51,83</t>
+          <t>-50,67; 51,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 13,22</t>
+          <t>-11,25; 12,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 23,66</t>
+          <t>-2,44; 24,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 11,62</t>
+          <t>-10,11; 11,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,72; 10,19</t>
+          <t>-26,46; 7,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-45,81; 100,56</t>
+          <t>-46,13; 99,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-18,34; 240,98</t>
+          <t>-13,47; 246,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-56,3; 159,23</t>
+          <t>-53,35; 148,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 300,89</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 13,98</t>
+          <t>-3,55; 14,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 10,54</t>
+          <t>-5,86; 11,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 6,71</t>
+          <t>-12,91; 6,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-24,18; 18,04</t>
+          <t>-23,3; 18,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 78,08</t>
+          <t>-14,57; 84,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-23,22; 49,17</t>
+          <t>-20,49; 55,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-38,32; 29,88</t>
+          <t>-38,63; 26,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-78,13; 194,56</t>
+          <t>-74,7; 180,18</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 12,57</t>
+          <t>-2,6; 13,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 7,66</t>
+          <t>-9,41; 7,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 6,23</t>
+          <t>-8,53; 5,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,33; 32,78</t>
+          <t>-27,38; 30,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 89,35</t>
+          <t>-13,1; 98,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-29,19; 33,89</t>
+          <t>-29,26; 33,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,3; 31,49</t>
+          <t>-32,82; 29,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,98; 95,63</t>
+          <t>-47,29; 80,62</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 6,9</t>
+          <t>-0,79; 6,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 6,12</t>
+          <t>-1,48; 5,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 2,79</t>
+          <t>-3,76; 3,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 8,7</t>
+          <t>-8,11; 9,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 37,04</t>
+          <t>-3,61; 37,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 35,59</t>
+          <t>-7,33; 34,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-18,51; 15,8</t>
+          <t>-17,62; 19,01</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-35,03; 56,66</t>
+          <t>-36,46; 62,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A02-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP18A02-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por control de salud periódico</t>
+          <t>Menores cuya última consulta médica fue por control de salud periódico</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,83</t>
+          <t>7,33</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>148,4%</t>
+          <t>148,58%</t>
         </is>
       </c>
     </row>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 32,42</t>
+          <t>0,6; 32,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 10,5</t>
+          <t>-14,18; 9,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,94; 1,57</t>
+          <t>-21,85; 1,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 34,07</t>
+          <t>-6,23; 33,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,33; 168,99</t>
+          <t>0,77; 167,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-56,99; 131,16</t>
+          <t>-64,56; 110,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-72,74; 14,46</t>
+          <t>-73,71; 12,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,95</t>
+          <t>4,23</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>41,49%</t>
         </is>
       </c>
     </row>
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 4,27</t>
+          <t>-10,54; 4,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 10,53</t>
+          <t>-4,78; 10,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 5,42</t>
+          <t>-11,82; 5,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,23; 22,82</t>
+          <t>-10,12; 26,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,56; 38,74</t>
+          <t>-53,16; 47,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,46; 134,87</t>
+          <t>-33,65; 153,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-60,77; 46,25</t>
+          <t>-60,87; 49,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-5,71</t>
+          <t>-5,02</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-53,71%</t>
+          <t>-50,23%</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 9,81</t>
+          <t>-13,42; 8,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 17,9</t>
+          <t>-5,35; 17,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 20,71</t>
+          <t>1,48; 20,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 11,49</t>
+          <t>-19,66; 9,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-46,77; 58,6</t>
+          <t>-50,89; 55,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,11; 135,27</t>
+          <t>-24,04; 142,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 520,01</t>
+          <t>-0,32; 401,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23,85</t>
+          <t>27,6</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>347,2%</t>
+          <t>450,17%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 14,09</t>
+          <t>-8,98; 13,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,02; 17,01</t>
+          <t>-0,08; 16,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 15,92</t>
+          <t>-2,3; 16,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 52,99</t>
+          <t>3,21; 58,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-36,14; 92,18</t>
+          <t>-36,82; 87,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 492,4</t>
+          <t>-6,47; 473,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,34; 276,97</t>
+          <t>-19,34; 309,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-22,32; —</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-20,17</t>
+          <t>-20,61</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1060,37 +1060,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,24; 15,28</t>
+          <t>-17,59; 17,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-26,49; -2,51</t>
+          <t>-26,13; -0,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,15; 11,97</t>
+          <t>-18,75; 13,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-54,91; 0,0</t>
+          <t>-55,51; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-58,3; 113,09</t>
+          <t>-59,94; 128,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-92,49; 8,95</t>
+          <t>-92,5; 19,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-50,67; 51,38</t>
+          <t>-51,2; 65,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-7,65</t>
+          <t>-10,16</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-48,58%</t>
+          <t>-61,15%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 12,9</t>
+          <t>-11,33; 14,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 24,52</t>
+          <t>-2,51; 22,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 11,52</t>
+          <t>-10,56; 11,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-26,46; 7,97</t>
+          <t>-29,09; 4,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,13; 99,72</t>
+          <t>-46,55; 98,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 246,06</t>
+          <t>-13,31; 248,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-53,35; 148,16</t>
+          <t>-56,48; 150,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 164,01</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-2,43</t>
+          <t>0,18</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-11,66%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 14,58</t>
+          <t>-4,27; 13,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 11,09</t>
+          <t>-7,27; 11,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 6,41</t>
+          <t>-13,29; 5,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-23,3; 18,25</t>
+          <t>-21,56; 19,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 84,77</t>
+          <t>-16,01; 77,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-20,49; 55,05</t>
+          <t>-25,27; 52,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-38,63; 26,49</t>
+          <t>-39,32; 22,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-74,7; 180,18</t>
+          <t>-75,23; 189,46</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>4,75</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 13,44</t>
+          <t>-3,13; 12,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 7,67</t>
+          <t>-8,83; 7,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 5,74</t>
+          <t>-8,42; 6,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,38; 30,32</t>
+          <t>-22,34; 34,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 98,06</t>
+          <t>-13,72; 91,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-29,26; 33,1</t>
+          <t>-28,43; 32,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,82; 29,26</t>
+          <t>-32,07; 32,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-47,29; 80,62</t>
+          <t>-39,26; 92,02</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>1,06</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 6,88</t>
+          <t>-0,4; 6,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 5,81</t>
+          <t>-1,41; 5,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 3,35</t>
+          <t>-4,07; 3,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 9,13</t>
+          <t>-7,7; 11,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 37,26</t>
+          <t>-1,47; 38,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 34,29</t>
+          <t>-6,74; 32,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-17,62; 19,01</t>
+          <t>-18,97; 19,2</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-36,46; 62,63</t>
+          <t>-32,43; 79,7</t>
         </is>
       </c>
     </row>
